--- a/output/StructureDefinition-provider-treatment-relationship-consent.xlsx
+++ b/output/StructureDefinition-provider-treatment-relationship-consent.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.1</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/output/StructureDefinition-provider-treatment-relationship-consent.xlsx
+++ b/output/StructureDefinition-provider-treatment-relationship-consent.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$68</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2261" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2476" uniqueCount="405">
   <si>
     <t>Property</t>
   </si>
@@ -551,16 +551,16 @@
 </t>
   </si>
   <si>
-    <t>Treatment relationship scope</t>
-  </si>
-  <si>
-    <t>Fixed to 'treatment' to indicate this consent represents a treatment relationship</t>
+    <t>Patient privacy / information disclosure scope</t>
+  </si>
+  <si>
+    <t>Fixed to 'patient-privacy' (Agreement to collect, access, use or disclose information). The Consent here is the provider's attestation that supports access to the patient's data via the Provider Access API; it is not a 'treatment' consent (which would be a patient's agreement to undergo a specific medical treatment).</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://terminology.hl7.org/CodeSystem/consentscope"/&gt;
-    &lt;code value="treatment"/&gt;
+    &lt;code value="patient-privacy"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -665,7 +665,7 @@
     <t>Practitioner, facility, or organization attesting to treatment relationship</t>
   </si>
   <si>
-    <t>The healthcare provider (practitioner, organization, or facility) attesting that they have a treatment relationship with the patient</t>
+    <t>The healthcare provider (practitioner, organization, or facility) attesting that they have a treatment relationship with the patient. The performer element SHOULD be populated using performer.identifier with the provider's NPI (National Provider Identifier) so that the attesting provider can be identified without requiring a FHIR resource reference on the receiving system.</t>
   </si>
   <si>
     <t>Commonly, the patient the consent pertains to is the consentor, but particularly for young and old people, it may be some other person - e.g. a legal guardian.</t>
@@ -678,6 +678,121 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Consent.performer.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Consent.performer.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Consent.performer.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>Consent.performer.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>Consent.performer.identifier</t>
+  </si>
+  <si>
+    <t>NPI or other identifier of the performing provider</t>
+  </si>
+  <si>
+    <t>The National Provider Identifier (NPI) or other business identifier of the practitioner, facility, or organization attesting to the treatment relationship. Using an identifier allows the provider to be identified without requiring a resolvable FHIR resource reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>Consent.performer.display</t>
+  </si>
+  <si>
+    <t>Display name of the performing provider</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>Consent.organization</t>
@@ -694,7 +809,7 @@
     <t>Organization responsible for the treatment relationship</t>
   </si>
   <si>
-    <t>The healthcare organization under which this treatment relationship exists</t>
+    <t>The healthcare organization under which this treatment relationship exists. Because the requester (provider/client) and the source/payer system maintain independent FHIR resource IDs, a literal `Reference.reference` value (e.g., `Organization/123`) is meaningful only inside the requester's system. To allow the source/payer to match the organization against its own records, the reference SHOULD be expressed as a *logical (identifier-based) reference* by populating `Reference.identifier` with a business identifier — typically the organization's NPI (`http://hl7.org/fhir/sid/us-npi`) — together with `Reference.display` for human readability. Alternatively, a `Reference.reference` MAY point to a `contained` Organization resource that itself carries the business identifier.</t>
   </si>
   <si>
     <t>FiveWs.witness</t>
@@ -735,29 +850,7 @@
     <t>Consent.policy.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Consent.policy.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Consent.policy.modifierExtension</t>
@@ -925,16 +1018,6 @@
     <t>Consent.provision.period.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Consent.provision.period.start</t>
   </si>
   <si>
@@ -1027,10 +1110,10 @@
 </t>
   </si>
   <si>
-    <t>Resource for the actor (or group, by role)</t>
-  </si>
-  <si>
-    <t>The resource that identifies the actor. To identify actors by type, use group to identify a set of actors by some property they share (e.g. 'admitting officers').</t>
+    <t>Identifier-based reference to the actor</t>
+  </si>
+  <si>
+    <t>Reference to the practitioner, organization, role, or care team involved in the treatment relationship. As with `Consent.organization`, a literal `Reference.reference` is meaningful only inside the requester's system. The reference SHOULD be expressed as a *logical (identifier-based) reference* by populating `Reference.identifier` with the actor's business identifier — typically the NPI (`http://hl7.org/fhir/sid/us-npi`) for Practitioner, PractitionerRole, or Organization actors — together with `Reference.display` for human readability, so that the source/payer system can match the actor against its own records without resolving a FHIR resource reference relative to the requester's system. Alternatively, the reference MAY point to a `contained` resource that itself carries the business identifier.</t>
   </si>
   <si>
     <t>Consent.provision.action</t>
@@ -1534,7 +1617,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN62"/>
+  <dimension ref="A1:AN68"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="33.671875" customWidth="true" bestFit="true"/>
@@ -3518,7 +3601,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>211</v>
       </c>
@@ -3527,7 +3610,7 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>212</v>
+        <v>80</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3537,22 +3620,22 @@
         <v>92</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3603,34 +3686,34 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>208</v>
+        <v>80</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>217</v>
       </c>
@@ -3639,35 +3722,35 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>220</v>
-      </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>141</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3705,46 +3788,46 @@
         <v>80</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>222</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>223</v>
       </c>
@@ -3760,27 +3843,29 @@
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J20" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I20" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -3829,16 +3914,16 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>104</v>
@@ -3850,7 +3935,7 @@
         <v>80</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>80</v>
@@ -3858,10 +3943,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3881,18 +3966,20 @@
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>228</v>
+        <v>106</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>232</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -3917,13 +4004,13 @@
         <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>80</v>
+        <v>234</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>80</v>
@@ -3941,7 +4028,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -3953,7 +4040,7 @@
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>80</v>
@@ -3962,50 +4049,50 @@
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>232</v>
+        <v>135</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>139</v>
+        <v>237</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>141</v>
+        <v>239</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4055,19 +4142,19 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>80</v>
@@ -4076,54 +4163,52 @@
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>138</v>
+        <v>212</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
       </c>
@@ -4171,19 +4256,19 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>80</v>
@@ -4198,16 +4283,16 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>80</v>
+        <v>248</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4217,22 +4302,22 @@
         <v>92</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>106</v>
+        <v>249</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4283,22 +4368,22 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>80</v>
+        <v>208</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>80</v>
@@ -4307,15 +4392,15 @@
         <v>80</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>80</v>
+        <v>252</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4329,25 +4414,25 @@
         <v>92</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>106</v>
+        <v>254</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4397,7 +4482,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4406,7 +4491,7 @@
         <v>92</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>104</v>
@@ -4415,7 +4500,7 @@
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>80</v>
+        <v>258</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>80</v>
@@ -4424,12 +4509,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4440,32 +4525,28 @@
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
@@ -4489,13 +4570,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>254</v>
+        <v>80</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>255</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -4513,16 +4594,16 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>104</v>
@@ -4540,12 +4621,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4556,25 +4637,25 @@
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
+        <v>214</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4625,19 +4706,19 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>215</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>80</v>
@@ -4646,7 +4727,7 @@
         <v>80</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -4654,21 +4735,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -4680,15 +4761,17 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>229</v>
+        <v>139</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>80</v>
@@ -4737,19 +4820,19 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
@@ -4758,7 +4841,7 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>80</v>
@@ -4766,14 +4849,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>137</v>
+        <v>266</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4786,24 +4869,26 @@
         <v>80</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>234</v>
+        <v>268</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
@@ -4851,7 +4936,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -4872,7 +4957,7 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>232</v>
+        <v>135</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>80</v>
@@ -4880,46 +4965,42 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4967,19 +5048,19 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
@@ -4988,18 +5069,18 @@
         <v>80</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5007,30 +5088,32 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>263</v>
+        <v>106</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5079,16 +5162,16 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
@@ -5106,12 +5189,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5125,25 +5208,29 @@
         <v>92</v>
       </c>
       <c r="H32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K32" t="s" s="2">
-        <v>267</v>
+        <v>170</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
@@ -5167,13 +5254,13 @@
         <v>80</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>80</v>
+        <v>284</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>80</v>
@@ -5191,7 +5278,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5200,7 +5287,7 @@
         <v>92</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>80</v>
+        <v>273</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>104</v>
@@ -5220,10 +5307,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5234,7 +5321,7 @@
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>93</v>
@@ -5243,16 +5330,16 @@
         <v>80</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>194</v>
+        <v>260</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5303,13 +5390,13 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
@@ -5330,12 +5417,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5349,22 +5436,22 @@
         <v>92</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>274</v>
+        <v>213</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>275</v>
+        <v>214</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5415,7 +5502,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>273</v>
+        <v>215</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5427,7 +5514,7 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
@@ -5436,7 +5523,7 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>80</v>
@@ -5444,21 +5531,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>80</v>
@@ -5470,15 +5557,17 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>228</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>229</v>
+        <v>139</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -5527,19 +5616,19 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
@@ -5548,7 +5637,7 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -5556,14 +5645,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>137</v>
+        <v>266</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5576,24 +5665,26 @@
         <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K36" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>234</v>
+        <v>268</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5641,7 +5732,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5662,54 +5753,50 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>232</v>
+        <v>135</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>138</v>
+        <v>292</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>238</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5757,19 +5844,19 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>240</v>
+        <v>291</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
@@ -5778,7 +5865,7 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -5786,10 +5873,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5809,16 +5896,16 @@
         <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>112</v>
+        <v>296</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5845,11 +5932,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -5867,7 +5956,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5896,10 +5985,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5919,16 +6008,16 @@
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>284</v>
+        <v>194</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5979,7 +6068,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6006,12 +6095,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6025,22 +6114,22 @@
         <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>229</v>
+        <v>303</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>230</v>
+        <v>304</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6091,7 +6180,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>231</v>
+        <v>302</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6103,7 +6192,7 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6112,7 +6201,7 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>232</v>
+        <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6120,21 +6209,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6146,17 +6235,15 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>138</v>
+        <v>212</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>139</v>
+        <v>213</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6193,31 +6280,31 @@
         <v>80</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>290</v>
+        <v>80</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -6226,50 +6313,50 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>293</v>
+        <v>139</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>294</v>
+        <v>218</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>295</v>
+        <v>141</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6319,28 +6406,28 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>296</v>
+        <v>222</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>298</v>
+        <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>299</v>
+        <v>216</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
@@ -6348,50 +6435,50 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>301</v>
+        <v>267</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q43" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6435,28 +6522,28 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>297</v>
+        <v>80</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>306</v>
+        <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>307</v>
+        <v>135</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -6478,7 +6565,7 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>93</v>
@@ -6487,10 +6574,10 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>309</v>
@@ -6503,35 +6590,31 @@
       <c r="P44" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q44" t="s" s="2">
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Y44" s="2"/>
+      <c r="Z44" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="R44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>80</v>
@@ -6555,7 +6638,7 @@
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>80</v>
@@ -6576,7 +6659,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>312</v>
       </c>
@@ -6595,22 +6678,22 @@
         <v>92</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>228</v>
+        <v>313</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>229</v>
+        <v>314</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>230</v>
+        <v>315</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6661,7 +6744,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>231</v>
+        <v>312</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6673,7 +6756,7 @@
         <v>80</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>80</v>
@@ -6682,7 +6765,7 @@
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>232</v>
+        <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>80</v>
@@ -6690,21 +6773,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>80</v>
@@ -6716,17 +6799,15 @@
         <v>80</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>138</v>
+        <v>212</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>139</v>
+        <v>213</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -6775,19 +6856,19 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>80</v>
@@ -6796,7 +6877,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -6804,14 +6885,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>237</v>
+        <v>137</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6824,26 +6905,24 @@
         <v>80</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>238</v>
+        <v>139</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="O47" t="s" s="2">
-        <v>147</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
@@ -6879,19 +6958,19 @@
         <v>80</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>80</v>
+        <v>220</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6912,7 +6991,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>135</v>
+        <v>216</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -6920,10 +6999,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6931,7 +7010,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>92</v>
@@ -6943,18 +7022,20 @@
         <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>321</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -6979,13 +7060,13 @@
         <v>80</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>318</v>
+        <v>80</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>319</v>
+        <v>80</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>80</v>
@@ -7003,16 +7084,16 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>104</v>
@@ -7021,21 +7102,21 @@
         <v>80</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>80</v>
+        <v>325</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7043,35 +7124,39 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="I49" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>80</v>
-      </c>
       <c r="K49" t="s" s="2">
-        <v>321</v>
+        <v>194</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q49" s="2"/>
+      <c r="Q49" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="R49" t="s" s="2">
         <v>80</v>
       </c>
@@ -7115,16 +7200,16 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>92</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>104</v>
@@ -7133,21 +7218,21 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>80</v>
+        <v>332</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>80</v>
+        <v>333</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7161,32 +7246,30 @@
         <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q50" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="R50" t="s" s="2">
         <v>80</v>
@@ -7207,13 +7290,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>329</v>
+        <v>80</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>331</v>
+        <v>80</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -7231,7 +7314,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7260,10 +7343,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7274,7 +7357,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
@@ -7283,20 +7366,18 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>333</v>
+        <v>212</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>334</v>
+        <v>213</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -7321,13 +7402,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>337</v>
+        <v>80</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>338</v>
+        <v>80</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -7345,19 +7426,19 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>332</v>
+        <v>215</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>80</v>
@@ -7366,13 +7447,13 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>339</v>
       </c>
@@ -7381,7 +7462,7 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7391,25 +7472,25 @@
         <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>333</v>
+        <v>138</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>340</v>
+        <v>139</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>341</v>
+        <v>218</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>342</v>
+        <v>141</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7435,11 +7516,13 @@
         <v>80</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>80</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>343</v>
+        <v>80</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>80</v>
@@ -7457,7 +7540,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>339</v>
+        <v>222</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -7469,7 +7552,7 @@
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
@@ -7478,7 +7561,7 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>80</v>
@@ -7486,14 +7569,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7506,24 +7589,26 @@
         <v>80</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>333</v>
+        <v>138</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>345</v>
+        <v>267</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>346</v>
+        <v>268</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
@@ -7547,13 +7632,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>348</v>
+        <v>80</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>349</v>
+        <v>80</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -7571,7 +7656,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>344</v>
+        <v>269</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -7583,7 +7668,7 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>143</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
@@ -7592,18 +7677,18 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7611,32 +7696,30 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>170</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -7661,13 +7744,13 @@
         <v>80</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>329</v>
+        <v>174</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
@@ -7685,13 +7768,13 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
@@ -7712,12 +7795,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7725,32 +7808,30 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>92</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>284</v>
+        <v>347</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -7799,10 +7880,10 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>92</v>
@@ -7828,10 +7909,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7854,21 +7935,23 @@
         <v>93</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>224</v>
+        <v>170</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q56" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="R56" t="s" s="2">
         <v>80</v>
@@ -7889,13 +7972,13 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>80</v>
+        <v>355</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>80</v>
+        <v>356</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>80</v>
+        <v>357</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -7913,7 +7996,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -7934,7 +8017,7 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>80</v>
@@ -7942,10 +8025,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7956,7 +8039,7 @@
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>80</v>
@@ -7965,18 +8048,20 @@
         <v>80</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>228</v>
+        <v>359</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>229</v>
+        <v>360</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -8001,13 +8086,13 @@
         <v>80</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>80</v>
+        <v>363</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>80</v>
+        <v>364</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -8025,19 +8110,19 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>231</v>
+        <v>358</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>80</v>
@@ -8046,13 +8131,13 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>232</v>
+        <v>80</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>365</v>
       </c>
@@ -8061,7 +8146,7 @@
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8071,25 +8156,25 @@
         <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>138</v>
+        <v>359</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>139</v>
+        <v>366</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>234</v>
+        <v>367</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>141</v>
+        <v>368</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8115,13 +8200,11 @@
         <v>80</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>80</v>
+        <v>369</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -8139,7 +8222,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>235</v>
+        <v>365</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8151,7 +8234,7 @@
         <v>80</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>80</v>
@@ -8160,7 +8243,7 @@
         <v>80</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>232</v>
+        <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>80</v>
@@ -8168,14 +8251,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8188,26 +8271,24 @@
         <v>80</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>138</v>
+        <v>359</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>238</v>
+        <v>371</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>239</v>
+        <v>372</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>373</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>80</v>
       </c>
@@ -8231,13 +8312,13 @@
         <v>80</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>80</v>
+        <v>174</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>80</v>
+        <v>374</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>80</v>
+        <v>375</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>80</v>
@@ -8255,7 +8336,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>240</v>
+        <v>370</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8267,7 +8348,7 @@
         <v>80</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>80</v>
@@ -8276,7 +8357,7 @@
         <v>80</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>80</v>
@@ -8284,10 +8365,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8295,10 +8376,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>80</v>
@@ -8310,15 +8391,17 @@
         <v>93</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -8343,13 +8426,13 @@
         <v>80</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>163</v>
+        <v>355</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>80</v>
@@ -8367,13 +8450,13 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>80</v>
@@ -8396,10 +8479,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8407,7 +8490,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>92</v>
@@ -8422,15 +8505,17 @@
         <v>93</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>373</v>
+        <v>313</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -8479,10 +8564,10 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>92</v>
@@ -8508,10 +8593,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8531,23 +8616,25 @@
         <v>80</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>83</v>
+        <v>260</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="Q62" s="2"/>
+      <c r="Q62" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="R62" t="s" s="2">
         <v>80</v>
       </c>
@@ -8591,7 +8678,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -8612,14 +8699,692 @@
         <v>80</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="AN62" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN62">
+  <autoFilter ref="A1:AN68">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8629,7 +9394,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI67">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
